--- a/artfynd/A 16122-2023 artfynd.xlsx
+++ b/artfynd/A 16122-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16122-2023 artfynd.xlsx
+++ b/artfynd/A 16122-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114670078</v>
+        <v>114670074</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485459</v>
+        <v>485654</v>
       </c>
       <c r="R2" t="n">
-        <v>6538112</v>
+        <v>6538140</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,6 +756,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>björkhögstubbe</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -780,16 +785,11 @@
         <v>114670075</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -887,12 +887,7 @@
         <v>118245474</v>
       </c>
       <c r="B4" t="n">
-        <v>97763</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,6 +1009,310 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126431766</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Korsning Gropbäcken Suttavägen, Finnafallsmossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>485414</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6538132</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Towe Jansson Genç</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Towe Jansson Genç</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114670073</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Finnafallsmossen, Ö om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>485702</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6538158</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-05-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-05-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114670078</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Finnafallsmossen, Ö om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>485459</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6538112</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-05-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-05-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16122-2023 artfynd.xlsx
+++ b/artfynd/A 16122-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114670074</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114670075</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118245474</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126431766</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114670073</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,8 +1343,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114670078</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>